--- a/ci-build/StructureDefinition-therapieziel-onkologie.xlsx
+++ b/ci-build/StructureDefinition-therapieziel-onkologie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T08:00:52+00:00</t>
+    <t>2026-05-04T08:07:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
